--- a/WorkBot/refactor/data/orders/US Foods/US Foods_Triphammer_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/US Foods/US Foods_Triphammer_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,66 +662,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1667864</t>
+          <t>4688660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Employee Water</t>
+          <t>Hals - Black Cherry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>35.60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4688660</t>
+          <t>5607194</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hals - Black Cherry</t>
+          <t>Hals - Lemon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.60</t>
+          <t>16.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5607194</t>
+          <t>6435380</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hals - Lemon</t>
+          <t>Hals - Lime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6435380</t>
+          <t>4858587</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hals - Lime</t>
+          <t>Hals - Original</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,51 +758,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>17.80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4858587</t>
+          <t>7196012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hals - Original</t>
+          <t>Bagel - Plain GF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>45.50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7196012</t>
+          <t>5614176</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagel - Plain GF</t>
+          <t>Bread - GF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,51 +812,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>43.49</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.50</t>
+          <t>86.98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5614176</t>
+          <t>3357597</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bread - GF</t>
+          <t>FRZ Fruit - Strawberry (Whole)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>86.98</t>
+          <t>43.74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3357597</t>
+          <t>4455234</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Strawberry (Whole)</t>
+          <t>Artichoke Hrt Qtrd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -866,12 +866,525 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>45.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7058803</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Can - Tomato - Whole Peeled</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>39.06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>78.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1026184</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Roasted Red Pepper (Strips)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>49.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3991049</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sausage - Italian Sweet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>65.68</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>65.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1365278</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vegan Chicken Tenders</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>87.80</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>87.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0490508</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brie</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>26.94</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>53.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7206874</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Can - Tomato (crushed)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>32.66</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>65.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7520950</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Can - Pizza Sauce</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>41.22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>82.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1035842</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Feta - Pail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>92.87</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>185.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3737152</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Honey - Jug</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>102.93</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>102.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7722184</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Parmesan (Grated)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>59.95</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>59.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5420690</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pork Butt (Bone In)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2212975</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Roast Beef (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>119.20</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>357.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3275539</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sauerkraut</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>58.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1025103</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Swiss (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>45.60</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>45.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8255796</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tuna White Chunk (Pouch)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>72.00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>432.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6364494</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Yogurt - Greek (Bulk)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>26.96</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>26.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4052171</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Apple Red - Fresh</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9546982</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Arugula - Fresh</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>81.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8457368</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Oil - Corn</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>76.10</t>
         </is>
       </c>
     </row>
